--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,6 +1273,240 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132021038</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rangeln, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>479928</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6597583</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132021014</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rangeln, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6597482</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131948035</v>
       </c>
       <c r="B2" t="n">
-        <v>58064</v>
+        <v>58066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>131946417</v>
       </c>
       <c r="B3" t="n">
-        <v>91802</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131945923</v>
       </c>
       <c r="B4" t="n">
-        <v>58064</v>
+        <v>58066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>131947343</v>
       </c>
       <c r="B5" t="n">
-        <v>91802</v>
+        <v>91804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131947805</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>132021038</v>
       </c>
       <c r="B7" t="n">
-        <v>57085</v>
+        <v>57086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>132021014</v>
       </c>
       <c r="B8" t="n">
-        <v>57085</v>
+        <v>57086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131948035</v>
       </c>
       <c r="B2" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>131946417</v>
       </c>
       <c r="B3" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>131945923</v>
       </c>
       <c r="B4" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>131947343</v>
       </c>
       <c r="B5" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131947805</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>132021038</v>
       </c>
       <c r="B7" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>132021014</v>
       </c>
       <c r="B8" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -675,61 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131948035</v>
+        <v>131946417</v>
       </c>
       <c r="B2" t="n">
-        <v>58071</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Slåmossen, Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480042</v>
+        <v>479988</v>
       </c>
       <c r="R2" t="n">
-        <v>6597501</v>
+        <v>6597660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131946417</v>
+        <v>131947343</v>
       </c>
       <c r="B3" t="n">
         <v>91809</v>
@@ -838,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479988</v>
+        <v>479984</v>
       </c>
       <c r="R3" t="n">
-        <v>6597660</v>
+        <v>6597644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131945923</v>
+        <v>132021038</v>
       </c>
       <c r="B4" t="n">
-        <v>58071</v>
+        <v>57091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,57 +900,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåmossen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479964</v>
+        <v>479928</v>
       </c>
       <c r="R4" t="n">
-        <v>6597673</v>
+        <v>6597583</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,27 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Filmsnutt finns.</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,57 +990,81 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131947343</v>
+        <v>132021014</v>
       </c>
       <c r="B5" t="n">
-        <v>91809</v>
+        <v>57091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slåmossen, Slåmossen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479984</v>
+        <v>480049</v>
       </c>
       <c r="R5" t="n">
-        <v>6597644</v>
+        <v>6597482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,22 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131947805</v>
+        <v>131948035</v>
       </c>
       <c r="B6" t="n">
-        <v>57909</v>
+        <v>58071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1187,21 +1161,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rangeln, Rangeln, Vstm</t>
+          <t>Slåmossen, Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480079</v>
+        <v>480042</v>
       </c>
       <c r="R6" t="n">
-        <v>6597395</v>
+        <v>6597501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1219,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färskt inhack i gran.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132021038</v>
+        <v>131945923</v>
       </c>
       <c r="B7" t="n">
-        <v>57091</v>
+        <v>58071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,53 +1262,57 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rangeln, Vstm</t>
+          <t>Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479928</v>
+        <v>479964</v>
       </c>
       <c r="R7" t="n">
-        <v>6597583</v>
+        <v>6597673</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,12 +1336,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Filmsnutt finns.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,22 +1371,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132021014</v>
+        <v>131947805</v>
       </c>
       <c r="B8" t="n">
-        <v>57091</v>
+        <v>57909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,16 +1394,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1426,31 +1421,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rangeln, Vstm</t>
+          <t>Rangeln, Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480049</v>
+        <v>480079</v>
       </c>
       <c r="R8" t="n">
-        <v>6597482</v>
+        <v>6597395</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,12 +1462,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färskt inhack i gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,12 +1497,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131946417</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131947343</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131948035</v>
       </c>
       <c r="B6" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131945923</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>132318242</v>
       </c>
       <c r="B9" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131946417</v>
       </c>
       <c r="B2" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131947343</v>
       </c>
       <c r="B3" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132021038</v>
       </c>
       <c r="B4" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>132021014</v>
       </c>
       <c r="B5" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131948035</v>
       </c>
       <c r="B6" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131945923</v>
       </c>
       <c r="B7" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>131947805</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>132318242</v>
       </c>
       <c r="B9" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131946417</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131947343</v>
       </c>
       <c r="B3" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132021038</v>
       </c>
       <c r="B4" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>132021014</v>
       </c>
       <c r="B5" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131948035</v>
       </c>
       <c r="B6" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131945923</v>
       </c>
       <c r="B7" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>131947805</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>132318242</v>
       </c>
       <c r="B9" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>132318242</v>
       </c>
       <c r="B9" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131946417</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131947343</v>
       </c>
       <c r="B3" t="n">
-        <v>91872</v>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,61 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132021038</v>
+        <v>132021050</v>
       </c>
       <c r="B4" t="n">
-        <v>57133</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479928</v>
+        <v>479885</v>
       </c>
       <c r="R4" t="n">
-        <v>6597583</v>
+        <v>6597624</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,27 +990,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132021014</v>
+        <v>131947805</v>
       </c>
       <c r="B5" t="n">
-        <v>57133</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,7 +1020,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1040,31 +1028,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rangeln, Vstm</t>
+          <t>Rangeln, Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480049</v>
+        <v>480079</v>
       </c>
       <c r="R5" t="n">
-        <v>6597482</v>
+        <v>6597395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,12 +1069,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färskt inhack i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,49 +1104,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131948035</v>
+        <v>132021014</v>
       </c>
       <c r="B6" t="n">
-        <v>58115</v>
+        <v>57153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1161,23 +1154,31 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåmossen, Slåmossen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480042</v>
+        <v>480049</v>
       </c>
       <c r="R6" t="n">
-        <v>6597501</v>
+        <v>6597482</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,27 +1205,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,80 +1225,76 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131945923</v>
+        <v>132021038</v>
       </c>
       <c r="B7" t="n">
-        <v>58115</v>
+        <v>57153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slåmossen, Vstm</t>
+          <t>Rangeln, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479964</v>
+        <v>479928</v>
       </c>
       <c r="R7" t="n">
-        <v>6597673</v>
+        <v>6597583</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,27 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Filmsnutt finns.</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131947805</v>
+        <v>131945923</v>
       </c>
       <c r="B8" t="n">
-        <v>57951</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,26 +1361,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1421,21 +1388,27 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rangeln, Rangeln, Vstm</t>
+          <t>Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480079</v>
+        <v>479964</v>
       </c>
       <c r="R8" t="n">
-        <v>6597395</v>
+        <v>6597673</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färskt inhack i gran.</t>
+          <t>Filmsnutt finns.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132318242</v>
+        <v>131948035</v>
       </c>
       <c r="B9" t="n">
-        <v>97990</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1542,19 +1515,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Slåmossen, Slåmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480025</v>
+        <v>480042</v>
       </c>
       <c r="R9" t="n">
-        <v>6597545</v>
+        <v>6597501</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,17 +1563,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1598,121 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132318242</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480025</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6597545</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14341-2026 artfynd.xlsx
+++ b/artfynd/A 14341-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131946417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947343</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132021050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947805</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132021014</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132021038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131945923</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131948035</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1713,8 +1758,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>